--- a/workbooks/Practice_Workbook_Aurelia_Grand.xlsx
+++ b/workbooks/Practice_Workbook_Aurelia_Grand.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Exercises" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Raw Data" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Assumptions" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Budget" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercises" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw Data" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -517,7 +517,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Fictional training data generated by Finance &amp; Commercial Training Simulator. Not real company or industry data.</t>
+          <t>Fictional training data generated by Finance Dojo. Not real company or industry data.</t>
         </is>
       </c>
     </row>
